--- a/docs/excel-migration/legacy-cases-export.xlsx
+++ b/docs/excel-migration/legacy-cases-export.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cases'!$A$1:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cases'!$A$1:$W$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,8 +67,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E1"/>
-        <bgColor rgb="00FFF8E1"/>
+        <fgColor rgb="00E3F2FD"/>
+        <bgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
     <fill>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -493,6 +493,14 @@
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -571,6 +579,46 @@
           <t>Remarks</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Family Type</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Economic Status</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Occupation</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Education Level</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Recidivism Before</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Recidivism After</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Family History of Crime</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -642,6 +690,38 @@
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>APL</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -717,6 +797,38 @@
           <t>First-time offender, family cooperative</t>
         </is>
       </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Labourer</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -792,6 +904,46 @@
           <t>Repeat offender — previous case closed</t>
         </is>
       </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>SingleParent</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Unemployed</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Class 5</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -863,6 +1015,38 @@
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>APL</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>Class 9</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -938,6 +1122,46 @@
           <t>Tribal welfare board involved</t>
         </is>
       </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Labourer</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1009,6 +1233,38 @@
           <t>Child in need of care — POCSO flagged</t>
         </is>
       </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>SingleParent</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>Domestic Help</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>Class 4</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1080,6 +1336,38 @@
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>APL</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>Class 11</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1151,6 +1439,38 @@
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>APL</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1226,6 +1546,46 @@
           <t>Land dispute related</t>
         </is>
       </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Unemployed</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1297,6 +1657,38 @@
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>Domestic Help</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>Class 7</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1368,6 +1760,46 @@
           <t>Weapon involved — high risk</t>
         </is>
       </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>SingleParent</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>Unemployed</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>Class 5</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1443,6 +1875,38 @@
           <t>Child labour rescue case</t>
         </is>
       </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>Labourer</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>Class 3</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1514,6 +1978,38 @@
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>APL</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1585,6 +2081,38 @@
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>Class 9</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1660,6 +2188,46 @@
           <t>First offence, tribal council mediation</t>
         </is>
       </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>Labourer</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1733,6 +2301,38 @@
           <t>Online fraud — digital literacy case</t>
         </is>
       </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>APL</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1800,9 +2400,41 @@
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>APL</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O18"/>
+  <autoFilter ref="A1:W18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1813,12 +2445,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1907,7 +2539,7 @@
           <t>beneficiaryAge</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>IMPORTED (optional)</t>
         </is>
@@ -1924,7 +2556,7 @@
           <t>beneficiaryContact</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>IMPORTED (optional)</t>
         </is>
@@ -1958,7 +2590,7 @@
           <t>offenceClassification</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>IMPORTED (enum mapped)</t>
         </is>
@@ -1975,7 +2607,7 @@
           <t>domicile</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>IMPORTED (enum mapped)</t>
         </is>
@@ -1992,7 +2624,7 @@
           <t>isFirstTimeOffender</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>IMPORTED (optional)</t>
         </is>
@@ -2001,100 +2633,236 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Case ID</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>LEGACY ONLY</t>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>IMPORTED (enum mapped)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Family Type</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>LEGACY ONLY</t>
+          <t>familyType</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>IMPORTED (enum mapped)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>Economic Status</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>LEGACY ONLY</t>
+          <t>economicStatus</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>IMPORTED (enum mapped)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Assigned Worker</t>
+          <t>Occupation</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>LEGACY ONLY</t>
+          <t>occupationText</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>INFORMATIONAL ONLY</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Date Registered</t>
+          <t>Education Level</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>LEGACY ONLY</t>
+          <t>educationLevelText</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>INFORMATIONAL ONLY</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>Recidivism Before</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>recidivismBeforeCount</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>IMPORTED (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Recidivism After</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>recidivismAfterCount</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>IMPORTED (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Family History of Crime</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>familyHistoryOfCrime</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>IMPORTED (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>LEGACY ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>LEGACY ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>LEGACY ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Assigned Worker</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>LEGACY ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Date Registered</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>LEGACY ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>LEGACY ONLY</t>
         </is>
